--- a/dynamical_DE_nonfid/cmb/lowl_litebird_fisher.xlsx
+++ b/dynamical_DE_nonfid/cmb/lowl_litebird_fisher.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41345.92559469578</v>
+        <v>26048.01451194545</v>
       </c>
       <c r="C2" t="n">
-        <v>-102893.4107531796</v>
+        <v>-62725.30984755469</v>
       </c>
       <c r="D2" t="n">
-        <v>25915.95414490661</v>
+        <v>16581.01653482757</v>
       </c>
       <c r="E2" t="n">
-        <v>27176.57381815277</v>
+        <v>18083.06765667289</v>
       </c>
       <c r="F2" t="n">
-        <v>-20816.76016644961</v>
+        <v>-13198.80642552863</v>
       </c>
       <c r="G2" t="n">
-        <v>-5692.076243354264</v>
+        <v>-3573.009738248722</v>
       </c>
       <c r="H2" t="n">
-        <v>-1159.650951145636</v>
+        <v>-733.5902603276788</v>
       </c>
       <c r="I2" t="n">
-        <v>5739.153218484187</v>
+        <v>15.83196062809316</v>
       </c>
       <c r="J2" t="n">
-        <v>-4997.55255829382</v>
+        <v>-3215.301657312298</v>
       </c>
       <c r="K2" t="n">
-        <v>-1346.903122813</v>
+        <v>-867.4878540631815</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-102893.4107531796</v>
+        <v>-62725.30984755469</v>
       </c>
       <c r="C3" t="n">
-        <v>298211.0361135384</v>
+        <v>192155.3529533907</v>
       </c>
       <c r="D3" t="n">
-        <v>-56992.22512458116</v>
+        <v>-32365.46367475746</v>
       </c>
       <c r="E3" t="n">
-        <v>-60807.70328324012</v>
+        <v>-37376.02068385682</v>
       </c>
       <c r="F3" t="n">
-        <v>48204.04768219112</v>
+        <v>28448.31072511405</v>
       </c>
       <c r="G3" t="n">
-        <v>13247.16726293276</v>
+        <v>7761.738257758881</v>
       </c>
       <c r="H3" t="n">
-        <v>2732.73959472569</v>
+        <v>1599.664850935546</v>
       </c>
       <c r="I3" t="n">
-        <v>-109278.7000355487</v>
+        <v>-94484.19266512901</v>
       </c>
       <c r="J3" t="n">
-        <v>11783.11748540148</v>
+        <v>7219.498360548522</v>
       </c>
       <c r="K3" t="n">
-        <v>3155.3460046823</v>
+        <v>1926.36479703576</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25915.95414490661</v>
+        <v>16581.01653482757</v>
       </c>
       <c r="C4" t="n">
-        <v>-56992.22512458116</v>
+        <v>-32365.46367475746</v>
       </c>
       <c r="D4" t="n">
-        <v>17990.47317421551</v>
+        <v>12233.80613896038</v>
       </c>
       <c r="E4" t="n">
-        <v>18037.62691269401</v>
+        <v>12532.4604872185</v>
       </c>
       <c r="F4" t="n">
-        <v>-13571.88316642511</v>
+        <v>-8946.733718929761</v>
       </c>
       <c r="G4" t="n">
-        <v>-3676.440893579613</v>
+        <v>-2394.96962815229</v>
       </c>
       <c r="H4" t="n">
-        <v>-778.2048835219516</v>
+        <v>-514.4280998893006</v>
       </c>
       <c r="I4" t="n">
-        <v>-15422.92455011993</v>
+        <v>-18888.1204614765</v>
       </c>
       <c r="J4" t="n">
-        <v>-3111.07664977044</v>
+        <v>-2050.186277989757</v>
       </c>
       <c r="K4" t="n">
-        <v>-845.3564488311912</v>
+        <v>-559.5190317173455</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27176.57381815277</v>
+        <v>18083.06765667289</v>
       </c>
       <c r="C5" t="n">
-        <v>-60807.70328324012</v>
+        <v>-37376.02068385682</v>
       </c>
       <c r="D5" t="n">
-        <v>18037.62691269401</v>
+        <v>12532.4604872185</v>
       </c>
       <c r="E5" t="n">
-        <v>19958.60129090614</v>
+        <v>14160.70967086235</v>
       </c>
       <c r="F5" t="n">
-        <v>-14663.51878658999</v>
+        <v>-9916.301279605046</v>
       </c>
       <c r="G5" t="n">
-        <v>-4013.433771068216</v>
+        <v>-2688.988151505273</v>
       </c>
       <c r="H5" t="n">
-        <v>-764.9886825437227</v>
+        <v>-521.5511144478266</v>
       </c>
       <c r="I5" t="n">
-        <v>-9799.813051260013</v>
+        <v>-13403.38633990055</v>
       </c>
       <c r="J5" t="n">
-        <v>-3543.038957360563</v>
+        <v>-2399.435732122837</v>
       </c>
       <c r="K5" t="n">
-        <v>-955.9843914171263</v>
+        <v>-649.2024283164542</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-20816.76016644961</v>
+        <v>-13198.80642552863</v>
       </c>
       <c r="C6" t="n">
-        <v>48204.04768219112</v>
+        <v>28448.31072511405</v>
       </c>
       <c r="D6" t="n">
-        <v>-13571.88316642511</v>
+        <v>-8946.733718929763</v>
       </c>
       <c r="E6" t="n">
-        <v>-14663.51878658999</v>
+        <v>-9916.301279605046</v>
       </c>
       <c r="F6" t="n">
-        <v>11017.57115192624</v>
+        <v>7101.484821989721</v>
       </c>
       <c r="G6" t="n">
-        <v>3019.285704998563</v>
+        <v>1927.848216574318</v>
       </c>
       <c r="H6" t="n">
-        <v>584.5150757876</v>
+        <v>377.7898223128481</v>
       </c>
       <c r="I6" t="n">
-        <v>4045.251801785382</v>
+        <v>7008.082392503878</v>
       </c>
       <c r="J6" t="n">
-        <v>2654.517111339633</v>
+        <v>1720.272874688228</v>
       </c>
       <c r="K6" t="n">
-        <v>716.012987262897</v>
+        <v>465.1696196857537</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5692.076243354265</v>
+        <v>-3573.009738248722</v>
       </c>
       <c r="C7" t="n">
-        <v>13247.16726293276</v>
+        <v>7761.738257758882</v>
       </c>
       <c r="D7" t="n">
-        <v>-3676.440893579613</v>
+        <v>-2394.96962815229</v>
       </c>
       <c r="E7" t="n">
-        <v>-4013.433771068216</v>
+        <v>-2688.988151505273</v>
       </c>
       <c r="F7" t="n">
-        <v>3019.285704998563</v>
+        <v>1927.848216574318</v>
       </c>
       <c r="G7" t="n">
-        <v>829.648367004204</v>
+        <v>525.0267493721923</v>
       </c>
       <c r="H7" t="n">
-        <v>158.1134679882003</v>
+        <v>100.9334299476364</v>
       </c>
       <c r="I7" t="n">
-        <v>837.5676609253351</v>
+        <v>1664.140064556332</v>
       </c>
       <c r="J7" t="n">
-        <v>733.3748323713681</v>
+        <v>471.2083981369911</v>
       </c>
       <c r="K7" t="n">
-        <v>197.5995343068433</v>
+        <v>127.2465473064161</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1159.650951145636</v>
+        <v>-733.5902603276788</v>
       </c>
       <c r="C8" t="n">
-        <v>2732.73959472569</v>
+        <v>1599.664850935546</v>
       </c>
       <c r="D8" t="n">
-        <v>-778.2048835219516</v>
+        <v>-514.4280998893006</v>
       </c>
       <c r="E8" t="n">
-        <v>-764.9886825437227</v>
+        <v>-521.5511144478266</v>
       </c>
       <c r="F8" t="n">
-        <v>584.5150757876</v>
+        <v>377.7898223128482</v>
       </c>
       <c r="G8" t="n">
-        <v>158.1134679882003</v>
+        <v>100.9334299476364</v>
       </c>
       <c r="H8" t="n">
-        <v>34.65280054696933</v>
+        <v>22.40950542389636</v>
       </c>
       <c r="I8" t="n">
-        <v>325.2506017821593</v>
+        <v>479.3601774017814</v>
       </c>
       <c r="J8" t="n">
-        <v>133.2401708885039</v>
+        <v>86.550961176596</v>
       </c>
       <c r="K8" t="n">
-        <v>36.18236845228678</v>
+        <v>23.5841939943954</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5739.153218484185</v>
+        <v>15.83196062809037</v>
       </c>
       <c r="C9" t="n">
-        <v>-109278.7000355487</v>
+        <v>-94484.19266512901</v>
       </c>
       <c r="D9" t="n">
-        <v>-15422.92455011993</v>
+        <v>-18888.1204614765</v>
       </c>
       <c r="E9" t="n">
-        <v>-9799.813051260011</v>
+        <v>-13403.38633990055</v>
       </c>
       <c r="F9" t="n">
-        <v>4045.251801785384</v>
+        <v>7008.082392503879</v>
       </c>
       <c r="G9" t="n">
-        <v>837.5676609253352</v>
+        <v>1664.140064556333</v>
       </c>
       <c r="H9" t="n">
-        <v>325.2506017821593</v>
+        <v>479.3601774017814</v>
       </c>
       <c r="I9" t="n">
-        <v>247128.9358368599</v>
+        <v>244882.1391176526</v>
       </c>
       <c r="J9" t="n">
-        <v>-83.28070098584399</v>
+        <v>628.2701843709996</v>
       </c>
       <c r="K9" t="n">
-        <v>39.64357936861533</v>
+        <v>230.5802518292076</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-4997.552558293819</v>
+        <v>-3215.301657312298</v>
       </c>
       <c r="C10" t="n">
-        <v>11783.11748540148</v>
+        <v>7219.498360548523</v>
       </c>
       <c r="D10" t="n">
-        <v>-3111.07664977044</v>
+        <v>-2050.186277989757</v>
       </c>
       <c r="E10" t="n">
-        <v>-3543.038957360563</v>
+        <v>-2399.435732122836</v>
       </c>
       <c r="F10" t="n">
-        <v>2654.517111339634</v>
+        <v>1720.272874688227</v>
       </c>
       <c r="G10" t="n">
-        <v>733.3748323713681</v>
+        <v>471.208398136991</v>
       </c>
       <c r="H10" t="n">
-        <v>133.2401708885039</v>
+        <v>86.55096117659602</v>
       </c>
       <c r="I10" t="n">
-        <v>-83.28070098584381</v>
+        <v>628.270184370999</v>
       </c>
       <c r="J10" t="n">
-        <v>670.6370835529432</v>
+        <v>439.5496142542542</v>
       </c>
       <c r="K10" t="n">
-        <v>179.9454980450654</v>
+        <v>118.0799144139202</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1346.903122812999</v>
+        <v>-867.4878540631815</v>
       </c>
       <c r="C11" t="n">
-        <v>3155.3460046823</v>
+        <v>1926.36479703576</v>
       </c>
       <c r="D11" t="n">
-        <v>-845.3564488311912</v>
+        <v>-559.5190317173455</v>
       </c>
       <c r="E11" t="n">
-        <v>-955.9843914171263</v>
+        <v>-649.2024283164543</v>
       </c>
       <c r="F11" t="n">
-        <v>716.012987262897</v>
+        <v>465.1696196857537</v>
       </c>
       <c r="G11" t="n">
-        <v>197.5995343068433</v>
+        <v>127.2465473064161</v>
       </c>
       <c r="H11" t="n">
-        <v>36.18236845228678</v>
+        <v>23.5841939943954</v>
       </c>
       <c r="I11" t="n">
-        <v>39.64357936861536</v>
+        <v>230.5802518292074</v>
       </c>
       <c r="J11" t="n">
-        <v>179.9454980450654</v>
+        <v>118.0799144139202</v>
       </c>
       <c r="K11" t="n">
-        <v>48.3250549976236</v>
+        <v>31.75881480839307</v>
       </c>
     </row>
   </sheetData>
